--- a/output/pdf_financials_xlsx/FNAU.xlsx
+++ b/output/pdf_financials_xlsx/FNAU.xlsx
@@ -1920,13 +1920,13 @@
         </is>
       </c>
       <c r="B92" s="3" t="n">
-        <v>0</v>
+        <v>0.419694</v>
       </c>
       <c r="C92" s="3" t="n">
-        <v>0</v>
+        <v>0.595979</v>
       </c>
       <c r="D92" s="3" t="n">
-        <v>0</v>
+        <v>0.549827</v>
       </c>
     </row>
     <row r="93">
@@ -3020,7 +3020,11 @@
           <t>Reserves (Note 7)</t>
         </is>
       </c>
-      <c r="D13" t="inlineStr"/>
+      <c r="D13" t="inlineStr">
+        <is>
+          <t>AdditionalPaidInCapital</t>
+        </is>
+      </c>
       <c r="E13" s="5" t="n">
         <v>0.419694</v>
       </c>

--- a/output/pdf_financials_xlsx/FNAU.xlsx
+++ b/output/pdf_financials_xlsx/FNAU.xlsx
@@ -980,13 +980,13 @@
         </is>
       </c>
       <c r="B34" s="3" t="n">
-        <v>0</v>
+        <v>0.02237</v>
       </c>
       <c r="C34" s="3" t="n">
-        <v>0</v>
+        <v>2.5e-05</v>
       </c>
       <c r="D34" s="3" t="n">
-        <v>0</v>
+        <v>0.004256</v>
       </c>
     </row>
     <row r="35">
@@ -1012,13 +1012,13 @@
         </is>
       </c>
       <c r="B36" s="3" t="n">
-        <v>0</v>
+        <v>0.02237</v>
       </c>
       <c r="C36" s="3" t="n">
-        <v>0</v>
+        <v>2.5e-05</v>
       </c>
       <c r="D36" s="3" t="n">
-        <v>0</v>
+        <v>0.004256</v>
       </c>
     </row>
     <row r="37">
@@ -1204,13 +1204,13 @@
         </is>
       </c>
       <c r="B48" s="3" t="n">
-        <v>0.034205</v>
+        <v>0.011835</v>
       </c>
       <c r="C48" s="3" t="n">
-        <v>2.5e-05</v>
+        <v>0</v>
       </c>
       <c r="D48" s="3" t="n">
-        <v>0.004256</v>
+        <v>0</v>
       </c>
     </row>
     <row r="49">
@@ -2689,7 +2689,7 @@
       </c>
       <c r="D2" t="inlineStr">
         <is>
-          <t>Cash</t>
+          <t>CashAndCashEquivalents</t>
         </is>
       </c>
       <c r="E2" s="5" t="n">

--- a/output/pdf_financials_xlsx/FNAU.xlsx
+++ b/output/pdf_financials_xlsx/FNAU.xlsx
@@ -2055,13 +2055,13 @@
         </is>
       </c>
       <c r="B101" s="3" t="n">
-        <v>0</v>
+        <v>0.000308</v>
       </c>
       <c r="C101" s="3" t="n">
-        <v>0</v>
+        <v>-0.014782</v>
       </c>
       <c r="D101" s="3" t="n">
-        <v>0</v>
+        <v>-0.006585</v>
       </c>
     </row>
     <row r="102">
@@ -2135,13 +2135,13 @@
         </is>
       </c>
       <c r="B106" s="3" t="n">
-        <v>0.194186</v>
+        <v>0.194494</v>
       </c>
       <c r="C106" s="3" t="n">
-        <v>0.266292</v>
+        <v>0.25151</v>
       </c>
       <c r="D106" s="3" t="n">
-        <v>0.277279</v>
+        <v>0.270694</v>
       </c>
     </row>
     <row r="107">
@@ -3367,7 +3367,11 @@
           <t>GST receivable</t>
         </is>
       </c>
-      <c r="D24" t="inlineStr"/>
+      <c r="D24" t="inlineStr">
+        <is>
+          <t>ChangeInReceivables</t>
+        </is>
+      </c>
       <c r="E24" s="5" t="n">
         <v>0.000308</v>
       </c>
@@ -3582,7 +3586,11 @@
           <t>Shares issued for cash</t>
         </is>
       </c>
-      <c r="D31" t="inlineStr"/>
+      <c r="D31" t="inlineStr">
+        <is>
+          <t>CommonStockIssuance</t>
+        </is>
+      </c>
       <c r="E31" s="5" t="n">
         <v>0.26205</v>
       </c>
@@ -4425,7 +4433,11 @@
           <t>Residual value of warrants that were part of units of a private placement $</t>
         </is>
       </c>
-      <c r="D58" t="inlineStr"/>
+      <c r="D58" t="inlineStr">
+        <is>
+          <t>CommonStockIssuance</t>
+        </is>
+      </c>
       <c r="E58" s="5" t="n">
         <v>0.01693</v>
       </c>
